--- a/zy71027/handovers_export.xlsx
+++ b/zy71027/handovers_export.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-24 06:14:35</t>
+          <t>2026-05-24 08:32:53</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>草稿</t>
+          <t>有冲突</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -542,7 +542,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-24 06:14:35</t>
+          <t>2026-05-24 08:32:53</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-24 06:14:35</t>
+          <t>2026-05-24 08:32:53</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-24 06:14:35</t>
+          <t>2026-05-24 08:32:53</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-24 06:14:35</t>
+          <t>2026-05-24 08:32:53</t>
         </is>
       </c>
     </row>
@@ -686,15 +686,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>草稿</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>赵药师</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-24 06:14:35</t>
+          <t>2026-05-24 08:32:53</t>
         </is>
       </c>
     </row>
@@ -966,7 +970,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
